--- a/input_data/admin_data/PER/_clean/total-pre-PER-adults.xlsx
+++ b/input_data/admin_data/PER/_clean/total-pre-PER-adults.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="12">
   <si>
     <t>year</t>
   </si>
